--- a/MitchIDPs.xlsx
+++ b/MitchIDPs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/malekshafei/Desktop/Louisville/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B713BB7D-A906-1D43-BA19-CD5EEDAE5B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F012371A-0ECA-ED45-9263-EEF413BF61FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6060" yWindow="500" windowWidth="28800" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="138">
   <si>
     <t>Player</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Overall</t>
   </si>
   <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
     <t>Bev &amp; Mitch</t>
   </si>
   <si>
@@ -423,13 +420,28 @@
   </si>
   <si>
     <t>AM</t>
+  </si>
+  <si>
+    <t>vs Palmerias</t>
+  </si>
+  <si>
+    <t>Combined</t>
+  </si>
+  <si>
+    <t>Bev</t>
+  </si>
+  <si>
+    <t>vs Lexington &amp; São Paolo</t>
+  </si>
+  <si>
+    <t>vs Lexington</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -458,6 +470,11 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -497,7 +514,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -508,6 +525,17 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -810,10 +838,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -841,148 +871,343 @@
     </row>
     <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="D2" s="5">
-        <v>45853</v>
+        <v>45867</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="4">
-        <v>2</v>
+      <c r="F2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G2" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D3" s="5">
-        <v>45853</v>
+        <v>45866</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>9</v>
+        <v>135</v>
       </c>
       <c r="F3" s="2"/>
-      <c r="G3" s="4">
-        <v>2</v>
+      <c r="G3" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D4" s="5">
-        <v>45853</v>
+        <v>45866</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>9</v>
+        <v>135</v>
       </c>
       <c r="F4" s="2"/>
-      <c r="G4" s="4">
-        <v>2</v>
+      <c r="G4" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D5" s="5">
-        <v>45853</v>
+        <v>45866</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>9</v>
+        <v>135</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="4">
-        <v>2</v>
+      <c r="G5" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D6" s="5">
-        <v>45853</v>
+        <v>45866</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>9</v>
+        <v>135</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="4">
-        <v>2</v>
+      <c r="G6" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="5">
+        <v>45866</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="5">
+        <v>45866</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="5">
+        <v>45861</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="5">
+        <v>45856</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G10" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C11" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="5">
         <v>45853</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="4">
+      <c r="F11" s="2"/>
+      <c r="G11" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" s="5">
+        <v>45853</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" s="5">
+        <v>45853</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" s="5">
+        <v>45853</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="5">
+        <v>45853</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" s="5">
+        <v>45853</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D17" s="10">
+        <v>45847</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2">
+      <c r="F17" s="2"/>
+      <c r="G17" s="9">
         <v>1</v>
       </c>
     </row>
@@ -1001,146 +1226,146 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>34</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>35</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>36</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I2" t="s">
         <v>37</v>
-      </c>
-      <c r="H2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I2" t="s">
-        <v>38</v>
       </c>
       <c r="J2">
         <v>11</v>
       </c>
       <c r="K2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s">
         <v>40</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>41</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>42</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>43</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>44</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I3" t="s">
         <v>45</v>
-      </c>
-      <c r="H3" t="s">
-        <v>132</v>
-      </c>
-      <c r="I3" t="s">
-        <v>46</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -1148,96 +1373,96 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
         <v>47</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>48</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>49</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
         <v>50</v>
       </c>
-      <c r="F4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" t="s">
-        <v>51</v>
-      </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J4">
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
         <v>52</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>53</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>54</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>55</v>
       </c>
-      <c r="E5" t="s">
-        <v>56</v>
-      </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J5">
         <v>5</v>
       </c>
       <c r="K5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -1245,49 +1470,49 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
         <v>57</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
         <v>58</v>
       </c>
-      <c r="D6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
         <v>59</v>
       </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" t="s">
-        <v>60</v>
-      </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J6">
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
@@ -1295,649 +1520,649 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
         <v>61</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>62</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>63</v>
       </c>
-      <c r="E7" t="s">
-        <v>64</v>
-      </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s">
         <v>45</v>
-      </c>
-      <c r="H7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" t="s">
-        <v>46</v>
       </c>
       <c r="J7">
         <v>12</v>
       </c>
       <c r="K7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
         <v>65</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>66</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>67</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>68</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" t="s">
         <v>69</v>
       </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" t="s">
-        <v>70</v>
-      </c>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J8">
         <v>26</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
         <v>71</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>72</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>73</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>74</v>
       </c>
-      <c r="E9" t="s">
-        <v>75</v>
-      </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J9">
         <v>34</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" t="s">
         <v>76</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>77</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>78</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>79</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" t="s">
         <v>80</v>
       </c>
-      <c r="F10" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" t="s">
-        <v>81</v>
-      </c>
       <c r="H10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J10">
         <v>14</v>
       </c>
       <c r="K10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
         <v>82</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>83</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" t="s">
         <v>84</v>
       </c>
-      <c r="D11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" t="s">
-        <v>85</v>
-      </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J11">
         <v>20</v>
       </c>
       <c r="K11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
         <v>86</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>87</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" t="s">
         <v>88</v>
       </c>
-      <c r="D12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" t="s">
-        <v>89</v>
-      </c>
       <c r="F12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J12">
         <v>8</v>
       </c>
       <c r="K12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" t="s">
         <v>90</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>91</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
         <v>92</v>
       </c>
-      <c r="D13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" t="s">
         <v>93</v>
       </c>
-      <c r="F13" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" t="s">
-        <v>94</v>
-      </c>
       <c r="H13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J13">
         <v>7</v>
       </c>
       <c r="K13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
         <v>95</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>96</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" t="s">
         <v>97</v>
       </c>
-      <c r="D14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>98</v>
       </c>
-      <c r="G14" t="s">
-        <v>99</v>
-      </c>
       <c r="H14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J14">
         <v>13</v>
       </c>
       <c r="K14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" t="s">
         <v>100</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>101</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>102</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>103</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" t="s">
         <v>104</v>
       </c>
-      <c r="F15" t="s">
-        <v>99</v>
-      </c>
-      <c r="G15" t="s">
-        <v>105</v>
-      </c>
       <c r="H15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J15">
         <v>16</v>
       </c>
       <c r="K15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" t="s">
         <v>106</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>107</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" t="s">
         <v>108</v>
       </c>
-      <c r="D16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" t="s">
-        <v>109</v>
-      </c>
       <c r="F16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J16">
         <v>42</v>
       </c>
       <c r="K16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" t="s">
         <v>110</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>111</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" t="s">
         <v>112</v>
       </c>
-      <c r="D17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>113</v>
       </c>
-      <c r="F17" t="s">
-        <v>114</v>
-      </c>
       <c r="G17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J17">
         <v>29</v>
       </c>
       <c r="K17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" t="s">
         <v>115</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>116</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" t="s">
         <v>117</v>
       </c>
-      <c r="D18" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" t="s">
         <v>118</v>
       </c>
-      <c r="F18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G18" t="s">
-        <v>119</v>
-      </c>
       <c r="H18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J18">
         <v>9</v>
       </c>
       <c r="K18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" t="s">
         <v>120</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>121</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" t="s">
         <v>122</v>
       </c>
-      <c r="D19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" t="s">
-        <v>123</v>
-      </c>
       <c r="F19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J19">
         <v>88</v>
       </c>
       <c r="K19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
@@ -1945,99 +2170,99 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" t="s">
         <v>124</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" t="s">
         <v>125</v>
       </c>
-      <c r="D20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" t="s">
-        <v>126</v>
-      </c>
       <c r="F20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J20">
         <v>6</v>
       </c>
       <c r="K20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" t="s">
         <v>127</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" t="s">
         <v>128</v>
       </c>
-      <c r="C21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" t="s">
-        <v>129</v>
-      </c>
       <c r="F21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J21">
         <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/MitchIDPs.xlsx
+++ b/MitchIDPs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,77 +468,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Allie George</t>
+          <t>Ellie Jean</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Combined</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bev</t>
+          <t>Mitch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>vs Palmerias</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ellie Jean</t>
+          <t>Bethany Balcer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Combined</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mitch</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>vs Palmerias</t>
-        </is>
-      </c>
+          <t>Bev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bethany Balcer</t>
+          <t>Kayla Fischer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -569,7 +565,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kayla Fischer</t>
+          <t>Sarah Weber</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -600,7 +596,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sarah Weber</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,7 +627,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Jordan Baggett</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -662,7 +658,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jordan Baggett</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -693,38 +689,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ella Hase</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Combined</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bev</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>Mitch</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>vs Lexington &amp; São Paolo</t>
+        </is>
+      </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>vs Lexington &amp; São Paolo</t>
+          <t>vs Lexington</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ella Hase</t>
+          <t>Bethany Balcer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -782,19 +782,15 @@
           <t>Mitch</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>vs Lexington</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bethany Balcer</t>
+          <t>Katie O'Kane</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -825,7 +821,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Katie O'Kane</t>
+          <t>Savannah DeMelo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -856,7 +852,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Savannah DeMelo</t>
+          <t>Uchenna Kanu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -887,7 +883,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Uchenna Kanu</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -918,7 +914,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Jordan Baggett</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -949,62 +945,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jordan Baggett</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mitch</t>
+          <t>Bev &amp; Mitch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ella Hase</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Video</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Bev &amp; Mitch</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
         <v>1</v>
       </c>
     </row>

--- a/MitchIDPs.xlsx
+++ b/MitchIDPs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,67 +468,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ellie Jean</t>
+          <t>Allie George</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Combined</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mitch</t>
+          <t>Bev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>vs Palmerias</t>
+          <t>abc</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bethany Balcer</t>
+          <t>Ellie Jean</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Combined</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bev</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>Mitch</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>vs Palmerias</t>
+        </is>
+      </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -689,42 +693,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Bethany Balcer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Combined</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mitch</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>vs Lexington &amp; São Paolo</t>
-        </is>
-      </c>
+          <t>Bev</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ella Hase</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>vs Lexington</t>
+          <t>vs Lexington &amp; São Paolo</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bethany Balcer</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -782,15 +782,19 @@
           <t>Mitch</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>vs Lexington</t>
+        </is>
+      </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Katie O'Kane</t>
+          <t>Bethany Balcer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -821,7 +825,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Savannah DeMelo</t>
+          <t>Katie O'Kane</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -852,7 +856,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Uchenna Kanu</t>
+          <t>Savannah DeMelo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -883,7 +887,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Uchenna Kanu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -914,7 +918,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jordan Baggett</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -945,31 +949,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ella Hase</t>
+          <t>Jordan Baggett</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bev &amp; Mitch</t>
+          <t>Mitch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ella Hase</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bev &amp; Mitch</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
         <v>1</v>
       </c>
     </row>

--- a/MitchIDPs.xlsx
+++ b/MitchIDPs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,77 +468,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Allie George</t>
+          <t>Ellie Jean</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Combined</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bev</t>
+          <t>Mitch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>abc</t>
+          <t>vs Palmerias</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ellie Jean</t>
+          <t>Kayla Fischer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Combined</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mitch</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>vs Palmerias</t>
-        </is>
-      </c>
+          <t>Bev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kayla Fischer</t>
+          <t>Sarah Weber</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -569,7 +565,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sarah Weber</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -600,7 +596,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Jordan Baggett</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,7 +627,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jordan Baggett</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -662,7 +658,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ella Hase</t>
+          <t>Bethany Balcer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -693,38 +689,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bethany Balcer</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Combined</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bev</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>Mitch</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>vs Lexington &amp; São Paolo</t>
+        </is>
+      </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>vs Lexington &amp; São Paolo</t>
+          <t>vs Lexington</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ella Hase</t>
+          <t>Bethany Balcer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -782,19 +782,15 @@
           <t>Mitch</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>vs Lexington</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bethany Balcer</t>
+          <t>Katie O'Kane</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -825,7 +821,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Katie O'Kane</t>
+          <t>Savannah DeMelo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -856,7 +852,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Savannah DeMelo</t>
+          <t>Uchenna Kanu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -887,7 +883,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Uchenna Kanu</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -918,7 +914,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Jordan Baggett</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -949,62 +945,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jordan Baggett</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mitch</t>
+          <t>Bev &amp; Mitch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ella Hase</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Video</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Bev &amp; Mitch</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
         <v>1</v>
       </c>
     </row>

--- a/MitchIDPs.xlsx
+++ b/MitchIDPs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,67 +468,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ellie Jean</t>
+          <t>Ary Borges</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Individual</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>1v1 Defending</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mitch</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>vs Palmerias</t>
+          <t>Pre Match - MD 17</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kayla Fischer</t>
+          <t>Ellie Jean</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Combined</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bev</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>Mitch</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>vs Palmerias</t>
+        </is>
+      </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -689,42 +693,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Kayla Fischer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Combined</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mitch</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>vs Lexington &amp; São Paolo</t>
-        </is>
-      </c>
+          <t>Bev</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ella Hase</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>vs Lexington</t>
+          <t>vs Lexington &amp; São Paolo</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bethany Balcer</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -782,15 +782,19 @@
           <t>Mitch</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>vs Lexington</t>
+        </is>
+      </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Katie O'Kane</t>
+          <t>Bethany Balcer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -821,7 +825,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Savannah DeMelo</t>
+          <t>Katie O'Kane</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -852,7 +856,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Uchenna Kanu</t>
+          <t>Savannah DeMelo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -883,7 +887,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Uchenna Kanu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -914,7 +918,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jordan Baggett</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -945,31 +949,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ella Hase</t>
+          <t>Jordan Baggett</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bev &amp; Mitch</t>
+          <t>Mitch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ella Hase</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bev &amp; Mitch</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
         <v>1</v>
       </c>
     </row>

--- a/MitchIDPs.xlsx
+++ b/MitchIDPs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,77 +468,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ary Borges</t>
+          <t>Ellie Jean</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1v1 Defending</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Mitch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pre Match - MD 17</t>
+          <t>vs Palmerias</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ellie Jean</t>
+          <t>Sarah Weber</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Combined</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mitch</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>vs Palmerias</t>
-        </is>
-      </c>
+          <t>Bev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sarah Weber</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -569,7 +565,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Jordan Baggett</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -600,7 +596,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jordan Baggett</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,7 +627,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ella Hase</t>
+          <t>Bethany Balcer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -662,7 +658,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bethany Balcer</t>
+          <t>Kayla Fischer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -693,38 +689,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kayla Fischer</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Combined</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bev</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>Mitch</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>vs Lexington &amp; São Paolo</t>
+        </is>
+      </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>vs Lexington &amp; São Paolo</t>
+          <t>vs Lexington</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ella Hase</t>
+          <t>Bethany Balcer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -782,19 +782,15 @@
           <t>Mitch</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>vs Lexington</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bethany Balcer</t>
+          <t>Katie O'Kane</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -825,7 +821,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Katie O'Kane</t>
+          <t>Savannah DeMelo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -856,7 +852,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Savannah DeMelo</t>
+          <t>Uchenna Kanu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -887,7 +883,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Uchenna Kanu</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -918,7 +914,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Jordan Baggett</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -949,62 +945,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jordan Baggett</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mitch</t>
+          <t>Bev &amp; Mitch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ella Hase</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Video</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Bev &amp; Mitch</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
         <v>1</v>
       </c>
     </row>

--- a/MitchIDPs.xlsx
+++ b/MitchIDPs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,67 +468,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ellie Jean</t>
+          <t>Courtney Petersen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Combined</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mitch</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>vs Palmerias</t>
-        </is>
-      </c>
+          <t>Bev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sarah Weber</t>
+          <t>Ellie Jean</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Combined</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bev</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>Mitch</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>vs Palmerias</t>
+        </is>
+      </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -689,42 +689,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Sarah Weber</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Combined</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mitch</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>vs Lexington &amp; São Paolo</t>
-        </is>
-      </c>
+          <t>Bev</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ella Hase</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -739,7 +735,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -749,32 +745,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>vs Lexington</t>
+          <t>vs Lexington &amp; São Paolo</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bethany Balcer</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -782,15 +778,19 @@
           <t>Mitch</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>vs Lexington</t>
+        </is>
+      </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Katie O'Kane</t>
+          <t>Bethany Balcer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Savannah DeMelo</t>
+          <t>Katie O'Kane</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -852,7 +852,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Uchenna Kanu</t>
+          <t>Savannah DeMelo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Uchenna Kanu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -914,7 +914,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jordan Baggett</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -945,31 +945,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ella Hase</t>
+          <t>Jordan Baggett</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bev &amp; Mitch</t>
+          <t>Mitch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ella Hase</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bev &amp; Mitch</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
         <v>1</v>
       </c>
     </row>

--- a/MitchIDPs.xlsx
+++ b/MitchIDPs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,73 +468,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Courtney Petersen</t>
+          <t>Ellie Jean</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Combined</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bev</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>Mitch</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>vs Palmerias</t>
+        </is>
+      </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ellie Jean</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Combined</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mitch</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>vs Palmerias</t>
-        </is>
-      </c>
+          <t>Bev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Jordan Baggett</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jordan Baggett</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ella Hase</t>
+          <t>Bethany Balcer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bethany Balcer</t>
+          <t>Kayla Fischer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -658,7 +658,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kayla Fischer</t>
+          <t>Sarah Weber</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -689,38 +689,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sarah Weber</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Combined</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bev</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>Mitch</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>vs Lexington &amp; São Paolo</t>
+        </is>
+      </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -735,7 +739,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -745,32 +749,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>vs Lexington &amp; São Paolo</t>
+          <t>vs Lexington</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ella Hase</t>
+          <t>Bethany Balcer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -778,19 +782,15 @@
           <t>Mitch</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>vs Lexington</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bethany Balcer</t>
+          <t>Katie O'Kane</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Katie O'Kane</t>
+          <t>Savannah DeMelo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -852,7 +852,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Savannah DeMelo</t>
+          <t>Uchenna Kanu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Uchenna Kanu</t>
+          <t>Marisa DiGrande</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -914,7 +914,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marisa DiGrande</t>
+          <t>Jordan Baggett</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -945,62 +945,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jordan Baggett</t>
+          <t>Ella Hase</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mitch</t>
+          <t>Bev &amp; Mitch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ella Hase</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Video</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Bev &amp; Mitch</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
         <v>1</v>
       </c>
     </row>
